--- a/inventory/files/2026-W42/STA_UK_AUTO_2026-W42.xlsx
+++ b/inventory/files/2026-W42/STA_UK_AUTO_2026-W42.xlsx
@@ -1694,7 +1694,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>13798</v>
+        <v>12875</v>
       </c>
     </row>
     <row r="10">
@@ -1704,7 +1704,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1128</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="11">
@@ -1714,7 +1714,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>726</v>
+        <v>366</v>
       </c>
     </row>
     <row r="12">
@@ -1724,7 +1724,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>370</v>
+        <v>240</v>
       </c>
     </row>
     <row r="13">
@@ -1734,7 +1734,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>231</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14">
@@ -1744,7 +1744,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
